--- a/samples/accessory_order.xlsx
+++ b/samples/accessory_order.xlsx
@@ -397,13 +397,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:H7"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -411,15 +414,24 @@
         <v>订单号</v>
       </c>
       <c r="B1" t="str">
-        <v>子件料号</v>
+        <v>物料代码</v>
       </c>
       <c r="C1" t="str">
-        <v>规格</v>
+        <v>物料名称</v>
       </c>
       <c r="D1" t="str">
-        <v>数量</v>
+        <v>规格型号</v>
       </c>
       <c r="E1" t="str">
+        <v>辅助属性</v>
+      </c>
+      <c r="F1" t="str">
+        <v>用量</v>
+      </c>
+      <c r="G1" t="str">
+        <v>单位</v>
+      </c>
+      <c r="H1" t="str">
         <v>备注</v>
       </c>
     </row>
@@ -431,13 +443,22 @@
         <v>C-A</v>
       </c>
       <c r="C2" t="str">
+        <v>配件管件</v>
+      </c>
+      <c r="D2" t="str">
         <v>1000mm</v>
       </c>
-      <c r="D2">
+      <c r="E2" t="str">
+        <v>镀锌</v>
+      </c>
+      <c r="F2">
         <v>2</v>
       </c>
-      <c r="E2" t="str">
-        <v>订单号需与总包订单一致</v>
+      <c r="G2" t="str">
+        <v>根</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -448,12 +469,21 @@
         <v>C-A</v>
       </c>
       <c r="C3" t="str">
+        <v>配件管件</v>
+      </c>
+      <c r="D3" t="str">
         <v>800mm</v>
       </c>
-      <c r="D3">
+      <c r="E3" t="str">
+        <v>镀锌</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
-      <c r="E3" t="str">
+      <c r="G3" t="str">
+        <v>根</v>
+      </c>
+      <c r="H3" t="str">
         <v/>
       </c>
     </row>
@@ -465,13 +495,22 @@
         <v>C-B</v>
       </c>
       <c r="C4" t="str">
+        <v>连接件</v>
+      </c>
+      <c r="D4" t="str">
         <v>标准</v>
       </c>
-      <c r="D4">
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4">
         <v>3</v>
       </c>
-      <c r="E4" t="str">
-        <v>数量须等于BOM对应子件数量</v>
+      <c r="G4" t="str">
+        <v>个</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -482,13 +521,22 @@
         <v>C-A</v>
       </c>
       <c r="C5" t="str">
+        <v>配件管件</v>
+      </c>
+      <c r="D5" t="str">
         <v>1000mm</v>
       </c>
-      <c r="D5">
+      <c r="E5" t="str">
+        <v>镀锌</v>
+      </c>
+      <c r="F5">
         <v>2</v>
       </c>
-      <c r="E5" t="str">
-        <v>此单示例数量不符会关联失败</v>
+      <c r="G5" t="str">
+        <v>根</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -499,12 +547,21 @@
         <v>C-A</v>
       </c>
       <c r="C6" t="str">
+        <v>配件管件</v>
+      </c>
+      <c r="D6" t="str">
         <v>800mm</v>
       </c>
-      <c r="D6">
+      <c r="E6" t="str">
+        <v>镀锌</v>
+      </c>
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="E6" t="str">
+      <c r="G6" t="str">
+        <v>根</v>
+      </c>
+      <c r="H6" t="str">
         <v/>
       </c>
     </row>
@@ -516,18 +573,27 @@
         <v>C-B</v>
       </c>
       <c r="C7" t="str">
+        <v>连接件</v>
+      </c>
+      <c r="D7" t="str">
         <v>标准</v>
       </c>
-      <c r="D7">
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7">
         <v>2</v>
       </c>
-      <c r="E7" t="str">
-        <v>BOM为3，这里故意写成2</v>
+      <c r="G7" t="str">
+        <v>个</v>
+      </c>
+      <c r="H7" t="str">
+        <v>故意数量不符示例</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
   </ignoredErrors>
 </worksheet>
 </file>